--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_14_10.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_14_10.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-54927.44711623243</v>
+        <v>-54919.5211930894</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24722807.49653043</v>
+        <v>24710253.95518699</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2675244.626997941</v>
+        <v>2680651.960846252</v>
       </c>
     </row>
     <row r="11">
@@ -22993,49 +22993,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>414.3580138970446</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H8" t="n">
-        <v>329.7996513619983</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I8" t="n">
-        <v>174.0544322839738</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J8" t="n">
-        <v>100.8636683457819</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K8" t="n">
-        <v>99.91746411030742</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L8" t="n">
-        <v>86.6819426081785</v>
+        <v>86.82148686318186</v>
       </c>
       <c r="M8" t="n">
-        <v>64.46103222224795</v>
+        <v>64.61630209323863</v>
       </c>
       <c r="N8" t="n">
-        <v>60.84366661166663</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O8" t="n">
-        <v>70.92290991414939</v>
+        <v>71.0718992657024</v>
       </c>
       <c r="P8" t="n">
-        <v>95.3805585693402</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q8" t="n">
-        <v>120.2861672613844</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R8" t="n">
-        <v>156.2415428392579</v>
+        <v>156.2970892917925</v>
       </c>
       <c r="S8" t="n">
-        <v>187.4921801390092</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T8" t="n">
-        <v>218.9603219259404</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U8" t="n">
-        <v>251.2700750183893</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,49 +23072,49 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>136.8380454650974</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H9" t="n">
-        <v>107.3536517836663</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I9" t="n">
-        <v>82.11907811320758</v>
+        <v>82.13536774255608</v>
       </c>
       <c r="J9" t="n">
-        <v>79.08163610062905</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K9" t="n">
-        <v>56.21884463473651</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L9" t="n">
-        <v>28.80272883647817</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M9" t="n">
-        <v>14.05903392201861</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22.33166897274658</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P9" t="n">
-        <v>37.45148288602854</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q9" t="n">
-        <v>75.45875521809711</v>
+        <v>75.51914927829571</v>
       </c>
       <c r="R9" t="n">
-        <v>114.2959190583036</v>
+        <v>114.3252943440434</v>
       </c>
       <c r="S9" t="n">
-        <v>162.2942560094982</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T9" t="n">
-        <v>198.1273230344443</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9081273639937</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,49 +23151,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.5672088666555</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H10" t="n">
-        <v>158.4594675894068</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I10" t="n">
-        <v>142.7065405010288</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J10" t="n">
-        <v>97.03484766890438</v>
+        <v>97.06289100487388</v>
       </c>
       <c r="K10" t="n">
-        <v>79.77883194102731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L10" t="n">
-        <v>71.88156152714005</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M10" t="n">
-        <v>72.49783312793308</v>
+        <v>72.56001021962938</v>
       </c>
       <c r="N10" t="n">
-        <v>62.83710184228248</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O10" t="n">
-        <v>78.55850566495766</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P10" t="n">
-        <v>86.47488929504939</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q10" t="n">
-        <v>116.0200016294459</v>
+        <v>116.0532158724207</v>
       </c>
       <c r="R10" t="n">
-        <v>158.2391290820876</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S10" t="n">
-        <v>216.6314341025461</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T10" t="n">
-        <v>226.1349336905766</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U10" t="n">
-        <v>286.2959146023925</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,49 +23230,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H11" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I11" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J11" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K11" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L11" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M11" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5890736468423086</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P11" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q11" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R11" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S11" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T11" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,19 +23309,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H12" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I12" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J12" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K12" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -23336,22 +23336,22 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R12" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S12" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T12" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U12" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,49 +23388,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H13" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I13" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J13" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K13" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L13" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M13" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N13" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O13" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P13" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q13" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R13" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S13" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T13" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,49 +23467,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H14" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I14" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J14" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K14" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L14" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M14" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5890736468421665</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P14" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q14" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R14" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S14" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T14" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,19 +23546,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H15" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I15" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J15" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K15" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -23573,22 +23573,22 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R15" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S15" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T15" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U15" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,49 +23625,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H16" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I16" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J16" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K16" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L16" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M16" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N16" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O16" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P16" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q16" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R16" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S16" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T16" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,49 +23704,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H17" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I17" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J17" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K17" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L17" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M17" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5890736468423086</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P17" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q17" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R17" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S17" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T17" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,19 +23783,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H18" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I18" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J18" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K18" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -23810,22 +23810,22 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R18" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S18" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T18" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U18" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,49 +23862,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H19" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I19" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J19" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K19" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L19" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M19" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N19" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O19" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P19" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q19" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R19" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S19" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T19" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,49 +23941,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H20" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I20" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J20" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K20" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L20" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M20" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5890736468423086</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P20" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q20" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R20" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S20" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T20" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,19 +24020,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H21" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I21" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J21" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K21" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -24047,22 +24047,22 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R21" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S21" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T21" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U21" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,49 +24099,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H22" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I22" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J22" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K22" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L22" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M22" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N22" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O22" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P22" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q22" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R22" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S22" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T22" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,49 +24178,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H23" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I23" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J23" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K23" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L23" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M23" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N23" t="n">
-        <v>0.589073646842337</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P23" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q23" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R23" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S23" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T23" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,19 +24257,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H24" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I24" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J24" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K24" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -24284,22 +24284,22 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R24" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S24" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T24" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U24" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,49 +24336,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H25" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I25" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J25" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K25" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L25" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M25" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N25" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O25" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P25" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q25" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R25" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S25" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T25" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,49 +24415,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H26" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I26" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J26" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K26" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L26" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M26" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N26" t="n">
-        <v>0.589073646842337</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P26" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q26" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R26" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S26" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T26" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,19 +24494,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H27" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I27" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J27" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K27" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -24521,22 +24521,22 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q27" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R27" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S27" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T27" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U27" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,49 +24573,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H28" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I28" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J28" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K28" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L28" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M28" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N28" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O28" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P28" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q28" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R28" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S28" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T28" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,49 +24652,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H29" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I29" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J29" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K29" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L29" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M29" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N29" t="n">
-        <v>0.589073646842337</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P29" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q29" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R29" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S29" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T29" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,19 +24731,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H30" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I30" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J30" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K30" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -24758,22 +24758,22 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q30" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R30" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S30" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T30" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U30" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,49 +24810,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H31" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I31" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J31" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K31" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L31" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M31" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N31" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O31" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P31" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q31" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R31" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S31" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T31" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,49 +24889,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H32" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I32" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J32" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K32" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L32" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M32" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N32" t="n">
-        <v>0.589073646842337</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P32" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q32" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R32" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S32" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T32" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,19 +24968,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H33" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I33" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J33" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K33" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -24995,22 +24995,22 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q33" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R33" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S33" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T33" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U33" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,49 +25047,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H34" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I34" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J34" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K34" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L34" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M34" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N34" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O34" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P34" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q34" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R34" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S34" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T34" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,49 +25126,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H35" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I35" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J35" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679383</v>
       </c>
       <c r="K35" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L35" t="n">
-        <v>33.3921737639572</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M35" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N35" t="n">
-        <v>0.589073646842337</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601003</v>
       </c>
       <c r="P35" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q35" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R35" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S35" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T35" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,19 +25205,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H36" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I36" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J36" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K36" t="n">
-        <v>27.04310878567982</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -25232,22 +25232,22 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q36" t="n">
-        <v>52.39520804828572</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R36" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S36" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T36" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U36" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,49 +25284,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H37" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I37" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J37" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K37" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L37" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M37" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N37" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O37" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P37" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q37" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R37" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S37" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T37" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,49 +25363,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H38" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I38" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J38" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K38" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L38" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M38" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N38" t="n">
-        <v>0.589073646842337</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P38" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q38" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R38" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S38" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T38" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,19 +25442,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H39" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I39" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J39" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K39" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -25469,22 +25469,22 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q39" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R39" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S39" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T39" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U39" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,49 +25521,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H40" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I40" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J40" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K40" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L40" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M40" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N40" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O40" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P40" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q40" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R40" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S40" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T40" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,49 +25600,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H41" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I41" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J41" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K41" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L41" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M41" t="n">
-        <v>5.165896543855752</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N41" t="n">
-        <v>0.589073646842337</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P41" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q41" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R41" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S41" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T41" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,19 +25679,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H42" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I42" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J42" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K42" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -25706,22 +25706,22 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q42" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R42" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S42" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T42" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U42" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,49 +25758,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H43" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I43" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J43" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K43" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L43" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M43" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N43" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O43" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P43" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q43" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R43" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S43" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T43" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,49 +25837,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.0203254548335</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H44" t="n">
-        <v>326.3412996032043</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I44" t="n">
-        <v>161.0356986156321</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J44" t="n">
-        <v>72.20278392367128</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K44" t="n">
-        <v>56.96222792940276</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L44" t="n">
-        <v>33.3921737639572</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M44" t="n">
-        <v>5.165896543855808</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5890736468423086</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>14.02620639656124</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P44" t="n">
-        <v>46.8205384688375</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q44" t="n">
-        <v>83.81961449756517</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R44" t="n">
-        <v>135.0292212312176</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S44" t="n">
-        <v>179.7971047621247</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T44" t="n">
-        <v>217.4820907701615</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2430599430124</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,19 +25916,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.6573662198144</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H45" t="n">
-        <v>105.6086706515908</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I45" t="n">
-        <v>75.89832339622643</v>
+        <v>75.83750674330533</v>
       </c>
       <c r="J45" t="n">
-        <v>62.01140968553466</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K45" t="n">
-        <v>27.04310878567982</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -25943,22 +25943,22 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.949671565273718</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q45" t="n">
-        <v>52.39520804828572</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R45" t="n">
-        <v>103.0779567941526</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S45" t="n">
-        <v>158.9382182736492</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T45" t="n">
-        <v>197.3990588835009</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U45" t="n">
-        <v>225.8962405715409</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,49 +25995,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4157334568194</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H46" t="n">
-        <v>157.1127134910461</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I46" t="n">
-        <v>138.1512618125042</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J46" t="n">
-        <v>86.32553619349451</v>
+        <v>86.2208375662932</v>
       </c>
       <c r="K46" t="n">
-        <v>62.18014341643709</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L46" t="n">
-        <v>49.36129923205802</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M46" t="n">
-        <v>48.75337411153957</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N46" t="n">
-        <v>39.65723298982337</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O46" t="n">
-        <v>57.14814500921987</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P46" t="n">
-        <v>68.15462699996738</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q46" t="n">
-        <v>103.3360016294459</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R46" t="n">
-        <v>151.4282438361859</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S46" t="n">
-        <v>213.9916308238575</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T46" t="n">
-        <v>225.4877205758225</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2876523073106</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>215364.7273311225</v>
+        <v>215170.9630151137</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>285365.8830580822</v>
+        <v>286009.7071515884</v>
       </c>
     </row>
   </sheetData>
@@ -26267,43 +26267,43 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>35894.12122185376</v>
+        <v>35861.82716918563</v>
       </c>
       <c r="E2" t="n">
-        <v>47560.98050968038</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="F2" t="n">
-        <v>47560.98050968037</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="G2" t="n">
-        <v>47560.98050968038</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="H2" t="n">
-        <v>47560.98050968038</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="I2" t="n">
-        <v>47560.98050968037</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="J2" t="n">
-        <v>47560.98050968037</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="K2" t="n">
-        <v>47560.98050968037</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="L2" t="n">
-        <v>47560.98050968037</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="M2" t="n">
-        <v>47560.98050968037</v>
+        <v>47668.28452526475</v>
       </c>
       <c r="N2" t="n">
-        <v>47560.98050968037</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="O2" t="n">
-        <v>47560.98050968038</v>
+        <v>47668.28452526476</v>
       </c>
       <c r="P2" t="n">
-        <v>47560.98050968037</v>
+        <v>47668.28452526477</v>
       </c>
     </row>
     <row r="3">
@@ -26319,10 +26319,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>201257.2899999996</v>
+        <v>201068.9115716352</v>
       </c>
       <c r="E3" t="n">
-        <v>67485.8520000002</v>
+        <v>68322.33943444483</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26423,43 +26423,43 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>38750.59999999999</v>
+        <v>38745.80483114667</v>
       </c>
       <c r="E5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="F5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="G5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="H5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="I5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="J5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="K5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="L5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="M5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="N5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="O5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="P5" t="n">
-        <v>6954.199999999995</v>
+        <v>6972.10256325733</v>
       </c>
     </row>
     <row r="6">
@@ -26475,43 +26475,43 @@
         <v>-33627.6</v>
       </c>
       <c r="D6" t="n">
-        <v>-204113.7687781458</v>
+        <v>-203952.8892335962</v>
       </c>
       <c r="E6" t="n">
-        <v>-26879.07149031982</v>
+        <v>-27626.1574724374</v>
       </c>
       <c r="F6" t="n">
-        <v>40606.78050968037</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="G6" t="n">
-        <v>40606.78050968038</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="H6" t="n">
-        <v>40606.78050968038</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="I6" t="n">
-        <v>40606.78050968037</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="J6" t="n">
-        <v>40606.78050968037</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="K6" t="n">
-        <v>40606.78050968037</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="L6" t="n">
-        <v>40606.78050968037</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="M6" t="n">
-        <v>40606.78050968037</v>
+        <v>40696.18196200742</v>
       </c>
       <c r="N6" t="n">
-        <v>40606.78050968037</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="O6" t="n">
-        <v>40606.78050968038</v>
+        <v>40696.18196200743</v>
       </c>
       <c r="P6" t="n">
-        <v>40606.78050968037</v>
+        <v>40696.18196200744</v>
       </c>
     </row>
   </sheetData>
@@ -26681,43 +26681,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>234.9999999999995</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="E3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="F3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="G3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="H3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="I3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="J3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="K3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="L3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="M3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="N3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="O3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="P3" t="n">
-        <v>318.9999999999998</v>
+        <v>319.8212184980426</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>235</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>85.04118037204844</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9447236180904495</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H8" t="n">
-        <v>9.67515075376882</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I8" t="n">
-        <v>36.42145728643209</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J8" t="n">
-        <v>80.18223618090437</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K8" t="n">
-        <v>120.1723869346731</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L8" t="n">
-        <v>149.0844723618087</v>
+        <v>148.9449281068054</v>
       </c>
       <c r="M8" t="n">
-        <v>165.8852010050248</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N8" t="n">
-        <v>168.5693969849243</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O8" t="n">
-        <v>159.1753015075373</v>
+        <v>159.0263121559843</v>
       </c>
       <c r="P8" t="n">
-        <v>135.8524371859293</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q8" t="n">
-        <v>102.0195226130651</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R8" t="n">
-        <v>59.34399497487426</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S8" t="n">
-        <v>21.52788944723614</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T8" t="n">
-        <v>4.135527638190945</v>
+        <v>4.131656751342871</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07557788944723595</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5054716981132065</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H9" t="n">
-        <v>4.881792452830179</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I9" t="n">
-        <v>17.40330188679242</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J9" t="n">
-        <v>47.75599056603765</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K9" t="n">
-        <v>81.62259433962248</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L9" t="n">
-        <v>109.751650943396</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M9" t="n">
-        <v>128.0749999999997</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>120.2645754716979</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P9" t="n">
-        <v>96.5229245283017</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q9" t="n">
-        <v>64.52301886792441</v>
+        <v>64.4626248077258</v>
       </c>
       <c r="R9" t="n">
-        <v>31.38358490566032</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S9" t="n">
-        <v>9.388915094339596</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T9" t="n">
-        <v>2.037405660377353</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03325471698113202</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4237704918032777</v>
+        <v>0.423373839243596</v>
       </c>
       <c r="H10" t="n">
-        <v>3.767704918032781</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I10" t="n">
-        <v>12.74393442622948</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J10" t="n">
-        <v>29.96057377049173</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K10" t="n">
-        <v>49.23442622950808</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L10" t="n">
-        <v>63.00311475409823</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M10" t="n">
-        <v>66.42795081967198</v>
+        <v>66.36577372797568</v>
       </c>
       <c r="N10" t="n">
-        <v>64.84844262295071</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O10" t="n">
-        <v>59.89803278688513</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P10" t="n">
-        <v>51.25311475409823</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q10" t="n">
-        <v>35.48499999999993</v>
+        <v>35.45178575702513</v>
       </c>
       <c r="R10" t="n">
-        <v>19.05426229508192</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S10" t="n">
-        <v>7.385163934426211</v>
+        <v>7.378251362090667</v>
       </c>
       <c r="T10" t="n">
-        <v>1.810655737704914</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02311475409836063</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H11" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I11" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J11" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K11" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L11" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M11" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N11" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P11" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q11" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R11" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S11" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T11" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,19 +31749,19 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H12" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I12" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J12" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K12" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q12" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R12" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S12" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T12" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H13" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I13" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J13" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K13" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L13" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M13" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N13" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O13" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P13" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R13" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S13" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T13" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H14" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I14" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J14" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K14" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L14" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M14" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N14" t="n">
-        <v>228.8239899497487</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P14" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q14" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R14" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S14" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T14" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,19 +31986,19 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H15" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I15" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J15" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K15" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q15" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R15" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S15" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T15" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H16" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I16" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J16" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K16" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L16" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M16" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N16" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O16" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P16" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R16" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S16" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T16" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H17" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I17" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J17" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K17" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L17" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M17" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N17" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P17" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q17" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R17" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S17" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T17" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,19 +32223,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H18" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I18" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J18" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K18" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
@@ -32250,22 +32250,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q18" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R18" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S18" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T18" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H19" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I19" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J19" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K19" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L19" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M19" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N19" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O19" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P19" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R19" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S19" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T19" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H20" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I20" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J20" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K20" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L20" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M20" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N20" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P20" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q20" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R20" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S20" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T20" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,19 +32460,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H21" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I21" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J21" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K21" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q21" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R21" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S21" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T21" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H22" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I22" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J22" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K22" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L22" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M22" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N22" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O22" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P22" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R22" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S22" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T22" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H23" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I23" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J23" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K23" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L23" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M23" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N23" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P23" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q23" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R23" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S23" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T23" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,19 +32697,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H24" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I24" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J24" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K24" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q24" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R24" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S24" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T24" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H25" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I25" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J25" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K25" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L25" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M25" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N25" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O25" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P25" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q25" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R25" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S25" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T25" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H26" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I26" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J26" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K26" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L26" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M26" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N26" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P26" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q26" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R26" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S26" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T26" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,19 +32934,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H27" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I27" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J27" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K27" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
@@ -32961,22 +32961,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q27" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R27" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S27" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T27" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H28" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I28" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J28" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K28" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L28" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M28" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N28" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O28" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P28" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q28" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R28" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S28" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T28" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U28" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H29" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I29" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J29" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K29" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L29" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M29" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N29" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P29" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q29" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R29" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S29" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T29" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,19 +33171,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H30" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I30" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J30" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K30" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L30" t="n">
         <v>138.5543797798742</v>
@@ -33198,22 +33198,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q30" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R30" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S30" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T30" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U30" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H31" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I31" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J31" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K31" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L31" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M31" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N31" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O31" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P31" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q31" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R31" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S31" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T31" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U31" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H32" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I32" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J32" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K32" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L32" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M32" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N32" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P32" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q32" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R32" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S32" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T32" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,19 +33408,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H33" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I33" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J33" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K33" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
@@ -33435,22 +33435,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q33" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R33" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S33" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T33" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U33" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H34" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I34" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J34" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K34" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L34" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M34" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N34" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O34" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P34" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q34" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R34" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S34" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T34" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U34" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H35" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I35" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J35" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K35" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L35" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M35" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N35" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P35" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q35" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R35" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S35" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T35" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,19 +33645,19 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H36" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I36" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J36" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K36" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L36" t="n">
         <v>138.5543797798742</v>
@@ -33672,22 +33672,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q36" t="n">
-        <v>87.58656603773579</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R36" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S36" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T36" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H37" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I37" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J37" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K37" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L37" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M37" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N37" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O37" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P37" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q37" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R37" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S37" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T37" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U37" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H38" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I38" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J38" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K38" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L38" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M38" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N38" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P38" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q38" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R38" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S38" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T38" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,19 +33882,19 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H39" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I39" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J39" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K39" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L39" t="n">
         <v>138.5543797798742</v>
@@ -33909,22 +33909,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q39" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R39" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S39" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T39" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U39" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H40" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I40" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J40" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K40" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L40" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M40" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N40" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O40" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P40" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q40" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R40" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S40" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T40" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U40" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H41" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I41" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J41" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K41" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L41" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M41" t="n">
-        <v>225.180336683417</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N41" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P41" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q41" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R41" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S41" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T41" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,19 +34119,19 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H42" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I42" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J42" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K42" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L42" t="n">
         <v>138.5543797798742</v>
@@ -34146,22 +34146,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q42" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R42" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S42" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T42" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U42" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H43" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I43" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J43" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K43" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L43" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M43" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N43" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O43" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P43" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q43" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R43" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S43" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T43" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U43" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.282412060301506</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H44" t="n">
-        <v>13.1335025125628</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I44" t="n">
-        <v>49.44019095477385</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J44" t="n">
-        <v>108.843120603015</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K44" t="n">
-        <v>163.1276231155778</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L44" t="n">
-        <v>202.37424120603</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M44" t="n">
-        <v>225.1803366834169</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N44" t="n">
-        <v>228.8239899497486</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>216.0720050251255</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P44" t="n">
-        <v>184.412457286432</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q44" t="n">
-        <v>138.4860753768843</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R44" t="n">
-        <v>80.55631658291452</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S44" t="n">
-        <v>29.22296482412059</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T44" t="n">
-        <v>5.613758793969843</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1025929648241204</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,19 +34356,19 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.686150943396226</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H45" t="n">
-        <v>6.626773584905657</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I45" t="n">
-        <v>23.62405660377357</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J45" t="n">
-        <v>64.82621698113203</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K45" t="n">
-        <v>110.7983301886792</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L45" t="n">
         <v>138.5543797798742</v>
@@ -34383,22 +34383,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>131.0247358490565</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q45" t="n">
-        <v>87.58656603773579</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R45" t="n">
-        <v>42.6015471698113</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S45" t="n">
-        <v>12.74495283018866</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T45" t="n">
-        <v>2.765669811320752</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04514150943396225</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5752459016393437</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H46" t="n">
-        <v>5.114459016393442</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I46" t="n">
-        <v>17.29921311475409</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J46" t="n">
-        <v>40.6698852459016</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K46" t="n">
-        <v>66.83311475409829</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L46" t="n">
-        <v>85.52337704918027</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M46" t="n">
-        <v>90.17240983606548</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N46" t="n">
-        <v>88.02831147540982</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O46" t="n">
-        <v>81.30839344262291</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P46" t="n">
-        <v>69.57337704918024</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q46" t="n">
-        <v>48.16899999999996</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R46" t="n">
-        <v>25.86514754098358</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S46" t="n">
-        <v>10.02496721311474</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T46" t="n">
-        <v>2.457868852459014</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U46" t="n">
-        <v>0.03137704918032788</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
